--- a/data/trans_orig/IP74A3_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP74A3_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto según si ha resuelto las cuotas de compras aplazadas en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Adultos según si tienen resuelto el retraso en los pagos de cuotas de compras aplazadas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>340</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3987</t>
+          <t>4172</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>473</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4457</t>
+          <t>4520</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7772</t>
+          <t>7590</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>78,74%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>666</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4480</t>
+          <t>4498</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>286</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4254</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7654</t>
+          <t>7809</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>81,02%</t>
         </is>
       </c>
     </row>
